--- a/test_template.xlsx
+++ b/test_template.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="근무기록_양식" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,21 +444,6 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>휴게시간</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>실근무시간</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>발생연장근로</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
           <t>사용연장근로</t>
         </is>
       </c>
@@ -486,54 +471,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>공휴일 (현충일)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>0</t>
         </is>
       </c>
     </row>
